--- a/artfynd/A 24826-2024 artfynd.xlsx
+++ b/artfynd/A 24826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676050</v>
+        <v>118676052</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654838</v>
+        <v>654828</v>
       </c>
       <c r="R2" t="n">
-        <v>7182395</v>
+        <v>7182394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676052</v>
+        <v>118676050</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654828</v>
+        <v>654838</v>
       </c>
       <c r="R3" t="n">
-        <v>7182394</v>
+        <v>7182395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676049</v>
+        <v>118676045</v>
       </c>
       <c r="B4" t="n">
         <v>79565</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654913</v>
+        <v>654789</v>
       </c>
       <c r="R4" t="n">
-        <v>7182350</v>
+        <v>7182526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676045</v>
+        <v>118676049</v>
       </c>
       <c r="B5" t="n">
         <v>79565</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654789</v>
+        <v>654913</v>
       </c>
       <c r="R5" t="n">
-        <v>7182526</v>
+        <v>7182350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24826-2024 artfynd.xlsx
+++ b/artfynd/A 24826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676052</v>
+        <v>118676050</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654828</v>
+        <v>654838</v>
       </c>
       <c r="R2" t="n">
-        <v>7182394</v>
+        <v>7182395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676050</v>
+        <v>118676045</v>
       </c>
       <c r="B3" t="n">
-        <v>79594</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654838</v>
+        <v>654789</v>
       </c>
       <c r="R3" t="n">
-        <v>7182395</v>
+        <v>7182526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676045</v>
+        <v>118676049</v>
       </c>
       <c r="B4" t="n">
         <v>79565</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654789</v>
+        <v>654913</v>
       </c>
       <c r="R4" t="n">
-        <v>7182526</v>
+        <v>7182350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676049</v>
+        <v>118676052</v>
       </c>
       <c r="B5" t="n">
         <v>79565</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654913</v>
+        <v>654828</v>
       </c>
       <c r="R5" t="n">
-        <v>7182350</v>
+        <v>7182394</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24826-2024 artfynd.xlsx
+++ b/artfynd/A 24826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118676050</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676045</v>
+        <v>118676052</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654789</v>
+        <v>654828</v>
       </c>
       <c r="R3" t="n">
-        <v>7182526</v>
+        <v>7182394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676049</v>
+        <v>118676045</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654913</v>
+        <v>654789</v>
       </c>
       <c r="R4" t="n">
-        <v>7182350</v>
+        <v>7182526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676052</v>
+        <v>118676049</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654828</v>
+        <v>654913</v>
       </c>
       <c r="R5" t="n">
-        <v>7182394</v>
+        <v>7182350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24826-2024 artfynd.xlsx
+++ b/artfynd/A 24826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676050</v>
+        <v>118676049</v>
       </c>
       <c r="B2" t="n">
-        <v>79601</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654838</v>
+        <v>654913</v>
       </c>
       <c r="R2" t="n">
-        <v>7182395</v>
+        <v>7182350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676052</v>
+        <v>118676045</v>
       </c>
       <c r="B3" t="n">
         <v>79572</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654828</v>
+        <v>654789</v>
       </c>
       <c r="R3" t="n">
-        <v>7182394</v>
+        <v>7182526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676045</v>
+        <v>118676052</v>
       </c>
       <c r="B4" t="n">
         <v>79572</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654789</v>
+        <v>654828</v>
       </c>
       <c r="R4" t="n">
-        <v>7182526</v>
+        <v>7182394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676049</v>
+        <v>118676050</v>
       </c>
       <c r="B5" t="n">
-        <v>79572</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654913</v>
+        <v>654838</v>
       </c>
       <c r="R5" t="n">
-        <v>7182350</v>
+        <v>7182395</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
